--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-blueberry_tiny_1.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-blueberry_tiny_1.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>57.10480189323425</v>
+        <v>116.5315692424774</v>
       </c>
       <c r="D2" t="n">
-        <v>6.539999961853027</v>
+        <v>15.47999954223633</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1470039426349103</v>
+        <v>0.470812013303792</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8834356069564819</v>
+        <v>0.907975435256958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7828418016433716</v>
+        <v>0.8564002513885498</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7766990065574646</v>
+        <v>0.7921225428581238</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7742837071418762</v>
+        <v>0.7877013087272644</v>
       </c>
       <c r="J2" t="n">
-        <v>0.103766955435276</v>
+        <v>0.1845151931047439</v>
       </c>
       <c r="K2" t="n">
-        <v>19.12963485717773</v>
+        <v>55.42530179023743</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0708183097839355</v>
+        <v>0.1051759481430053</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1263781356811523</v>
+        <v>0.5021372127532959</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1303306436538696</v>
+        <v>0.2058170509338379</v>
       </c>
       <c r="O2" t="n">
-        <v>3.540915489196777</v>
+        <v>5.258797407150269</v>
       </c>
       <c r="P2" t="n">
-        <v>6.318906784057617</v>
+        <v>25.10686063766479</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.516532182693481</v>
+        <v>10.2908525466919</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-155136</t>
+          <t>20250725-221537</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>63.41537308692932</v>
+        <v>85.64417839050293</v>
       </c>
       <c r="D3" t="n">
-        <v>6.510000228881836</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1453375029000075</v>
+        <v>0.4725706348052391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8679245114326477</v>
+        <v>0.8987341523170471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8134714961051941</v>
+        <v>0.8478405475616455</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8145266175270081</v>
+        <v>0.8466756939888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8190599083900452</v>
+        <v>0.8418230414390564</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0896379575133323</v>
+        <v>0.185072511434555</v>
       </c>
       <c r="K3" t="n">
-        <v>19.93363475799561</v>
+        <v>54.87039947509766</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06799694538116451</v>
+        <v>0.1085694313049316</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1236702489852905</v>
+        <v>0.5070796489715577</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1328284692764282</v>
+        <v>0.2112047147750854</v>
       </c>
       <c r="O3" t="n">
-        <v>3.399847269058228</v>
+        <v>5.428471565246582</v>
       </c>
       <c r="P3" t="n">
-        <v>6.183512449264526</v>
+        <v>25.35398244857788</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.641423463821411</v>
+        <v>10.56023573875427</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-155348</t>
+          <t>20250725-221959</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>60.20433855056763</v>
+        <v>85.53137016296387</v>
       </c>
       <c r="D4" t="n">
-        <v>6.510000228881836</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1436695421951404</v>
+        <v>0.4708236715732476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8819875717163086</v>
+        <v>0.8987341523170471</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8049254417419434</v>
+        <v>0.8378208875656128</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8041504621505737</v>
+        <v>0.7853479981422424</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7950713634490967</v>
+        <v>0.7861866354942322</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1000428572297096</v>
+        <v>0.1844363659620285</v>
       </c>
       <c r="K4" t="n">
-        <v>19.32123780250549</v>
+        <v>79.98272848129272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0630412340164184</v>
+        <v>0.1179649209976196</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1313858699798584</v>
+        <v>0.5038505554199219</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1303719043731689</v>
+        <v>0.2101810884475708</v>
       </c>
       <c r="O4" t="n">
-        <v>3.152061700820923</v>
+        <v>5.898246049880981</v>
       </c>
       <c r="P4" t="n">
-        <v>6.56929349899292</v>
+        <v>25.19252777099609</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.518595218658447</v>
+        <v>10.50905442237854</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-155607</t>
+          <t>20250725-222349</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>47.30350089073181</v>
+        <v>75.01971411705017</v>
       </c>
       <c r="D5" t="n">
-        <v>6.510000228881836</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1448302696700449</v>
+        <v>0.4714217475231956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8662420511245728</v>
+        <v>0.9135802388191224</v>
       </c>
       <c r="G5" t="n">
-        <v>0.803396463394165</v>
+        <v>0.8325963616371155</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8028720617294312</v>
+        <v>0.8114126920700073</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7982062697410583</v>
+        <v>0.8125</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1026168838143348</v>
+        <v>0.1804208010435104</v>
       </c>
       <c r="K5" t="n">
-        <v>19.51875257492065</v>
+        <v>73.0395667552948</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0730934810638427</v>
+        <v>0.1019962215423583</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1297949695587158</v>
+        <v>0.5016196680068969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1316215562820434</v>
+        <v>0.206022834777832</v>
       </c>
       <c r="O5" t="n">
-        <v>3.654674053192138</v>
+        <v>5.09981107711792</v>
       </c>
       <c r="P5" t="n">
-        <v>6.489748477935791</v>
+        <v>25.08098340034485</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.581077814102173</v>
+        <v>10.3011417388916</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-155822</t>
+          <t>20250725-222806</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>48.10929942131042</v>
+        <v>89.51973724365234</v>
       </c>
       <c r="D6" t="n">
-        <v>6.53000020980835</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1446521966545669</v>
+        <v>0.4714393027317829</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8930817842483521</v>
+        <v>0.8974359035491943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8039734959602356</v>
+        <v>0.8205461502075195</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7673048377037048</v>
+        <v>0.76877760887146</v>
       </c>
       <c r="I6" t="n">
-        <v>0.767870306968689</v>
+        <v>0.7696835994720459</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1155830696225166</v>
+        <v>0.1879550963640213</v>
       </c>
       <c r="K6" t="n">
-        <v>19.33374428749084</v>
+        <v>74.64021229743958</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06437265872955319</v>
+        <v>0.1131266450881958</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1251251649856567</v>
+        <v>0.5052678251266479</v>
       </c>
       <c r="N6" t="n">
-        <v>0.130143027305603</v>
+        <v>0.2148752784729004</v>
       </c>
       <c r="O6" t="n">
-        <v>3.218632936477661</v>
+        <v>5.65633225440979</v>
       </c>
       <c r="P6" t="n">
-        <v>6.256258249282837</v>
+        <v>25.2633912563324</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.507151365280151</v>
+        <v>10.74376392364502</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-160025</t>
+          <t>20250725-223204</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>116.5795435905456</v>
+        <v>337.2809314727783</v>
       </c>
       <c r="D2" t="n">
-        <v>9.880000114440918</v>
+        <v>20.57999992370605</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2900333262008169</v>
+        <v>0.5423713718851407</v>
       </c>
       <c r="F2" t="n">
-        <v>0.912500023841858</v>
+        <v>0.7586206793785095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8454963564872742</v>
+        <v>0.682692289352417</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7837638258934021</v>
+        <v>0.6858288645744324</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7813194990158081</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1320323795080185</v>
+        <v>0.1651308089494705</v>
       </c>
       <c r="K2" t="n">
-        <v>117.5288558006287</v>
+        <v>75.82084083557129</v>
       </c>
       <c r="L2" t="n">
-        <v>0.110161108970642</v>
+        <v>0.1176994466781616</v>
       </c>
       <c r="M2" t="n">
-        <v>0.508878788948059</v>
+        <v>0.2462745428085327</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2121941328048706</v>
+        <v>0.2202498912811279</v>
       </c>
       <c r="O2" t="n">
-        <v>5.508055448532104</v>
+        <v>5.884972333908081</v>
       </c>
       <c r="P2" t="n">
-        <v>25.44393944740296</v>
+        <v>12.31372714042664</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.60970664024353</v>
+        <v>11.0124945640564</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-054102</t>
+          <t>20250724-143132</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>69.79542231559753</v>
+        <v>358.9647183418274</v>
       </c>
       <c r="D3" t="n">
-        <v>9.760000228881836</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2902077826169821</v>
+        <v>0.518932361404101</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8961039185523987</v>
+        <v>0.8322981595993042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8514977693557739</v>
+        <v>0.8124602437019348</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7089611291885376</v>
+        <v>0.7929077744483948</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7007182836532593</v>
+        <v>0.780802309513092</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1266395598649978</v>
+        <v>0.1851205378770828</v>
       </c>
       <c r="K3" t="n">
-        <v>97.63745975494383</v>
+        <v>81.75956273078918</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1105159664154052</v>
+        <v>0.1193452644348144</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5074609851837159</v>
+        <v>0.2524397230148315</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2115824127197265</v>
+        <v>0.2506147718429565</v>
       </c>
       <c r="O3" t="n">
-        <v>5.525798320770264</v>
+        <v>5.967263221740723</v>
       </c>
       <c r="P3" t="n">
-        <v>25.37304925918579</v>
+        <v>12.62198615074158</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.57912063598633</v>
+        <v>12.53073859214783</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-054634</t>
+          <t>20250724-144007</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n">
-        <v>83.71411871910095</v>
+        <v>381.0303111076355</v>
       </c>
       <c r="D4" t="n">
-        <v>9.800000190734863</v>
+        <v>21.04000091552734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2901510596275329</v>
+        <v>0.5229920391853039</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8944099545478821</v>
+        <v>0.9012345671653748</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8614640235900879</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8257887363433838</v>
+        <v>0.8580771684646606</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8262069225311279</v>
+        <v>0.8545095324516296</v>
       </c>
       <c r="J4" t="n">
-        <v>0.126919686794281</v>
+        <v>0.1618397682905197</v>
       </c>
       <c r="K4" t="n">
-        <v>93.83553266525269</v>
+        <v>82.45394420623779</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1074251747131347</v>
+        <v>0.1090468978881836</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5085902214050293</v>
+        <v>0.2468412113189697</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2172157096862793</v>
+        <v>0.2543173742294311</v>
       </c>
       <c r="O4" t="n">
-        <v>5.371258735656738</v>
+        <v>5.45234489440918</v>
       </c>
       <c r="P4" t="n">
-        <v>25.42951107025146</v>
+        <v>12.34206056594849</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.86078548431396</v>
+        <v>12.71586871147156</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-055054</t>
+          <t>20250724-144854</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>50.6654543876648</v>
+        <v>414.7677924633026</v>
       </c>
       <c r="D5" t="n">
-        <v>9.779999732971191</v>
+        <v>19.36000061035156</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2886155812904752</v>
+        <v>0.5436705169645516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9024389982223512</v>
+        <v>0.8181818127632141</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8331226110458374</v>
+        <v>0.8012698292732239</v>
       </c>
       <c r="H5" t="n">
-        <v>0.823050856590271</v>
+        <v>0.7644128203392029</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8202323913574219</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1244431808590889</v>
+        <v>0.1662873476743698</v>
       </c>
       <c r="K5" t="n">
-        <v>93.79318332672121</v>
+        <v>82.92108058929443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1132250547409057</v>
+        <v>0.1233313941955566</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5075372552871704</v>
+        <v>0.2459057378768921</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2119218063354492</v>
+        <v>0.228105993270874</v>
       </c>
       <c r="O5" t="n">
-        <v>5.661252737045288</v>
+        <v>6.166569709777832</v>
       </c>
       <c r="P5" t="n">
-        <v>25.37686276435852</v>
+        <v>12.2952868938446</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.59609031677246</v>
+        <v>11.4052996635437</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-055525</t>
+          <t>20250724-145804</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
-        <v>89.60327935218811</v>
+        <v>401.5580163002014</v>
       </c>
       <c r="D6" t="n">
-        <v>9.829999923706056</v>
+        <v>20.8799991607666</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2903341706152315</v>
+        <v>0.5395800467223337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.887499988079071</v>
+        <v>0.7530864477157593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8306666612625122</v>
+        <v>0.7252897024154663</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8251181840896606</v>
+        <v>0.7364818453788757</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8225696682929993</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1278164237737655</v>
+        <v>0.1718398332595825</v>
       </c>
       <c r="K6" t="n">
-        <v>95.88123631477356</v>
+        <v>76.73413610458374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1174443817138671</v>
+        <v>0.1235195207595825</v>
       </c>
       <c r="M6" t="n">
-        <v>0.510363564491272</v>
+        <v>0.25016028881073</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2166830587387085</v>
+        <v>0.2406151819229126</v>
       </c>
       <c r="O6" t="n">
-        <v>5.872219085693359</v>
+        <v>6.175976037979126</v>
       </c>
       <c r="P6" t="n">
-        <v>25.5181782245636</v>
+        <v>12.5080144405365</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.83415293693542</v>
+        <v>12.03075909614563</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-055922</t>
+          <t>20250724-150757</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C2" t="n">
-        <v>369.64999127388</v>
+        <v>382.0909774303436</v>
       </c>
       <c r="D2" t="n">
-        <v>14.05000019073486</v>
+        <v>9.939999580383301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4832698102317639</v>
+        <v>0.3728636361849614</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.8982036113739014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8084577322006226</v>
+        <v>0.8493859171867371</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8015666007995605</v>
+        <v>0.8434048295021057</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2722620368003845</v>
+        <v>0.8346951603889465</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1638714224100113</v>
+        <v>0.1724959313869476</v>
       </c>
       <c r="K2" t="n">
-        <v>82.48740839958191</v>
+        <v>45.4380624294281</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1325806236267089</v>
+        <v>0.1205277299880981</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2438326978683471</v>
+        <v>0.2729627799987792</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2329417037963867</v>
+        <v>0.2303254461288452</v>
       </c>
       <c r="O2" t="n">
-        <v>6.629031181335449</v>
+        <v>6.026386499404907</v>
       </c>
       <c r="P2" t="n">
-        <v>12.19163489341736</v>
+        <v>13.64813899993896</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.64708518981934</v>
+        <v>11.51627230644226</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-113549</t>
+          <t>20250727-001019</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>328.5558805465698</v>
+        <v>242.773472070694</v>
       </c>
       <c r="D3" t="n">
-        <v>14.39999961853027</v>
+        <v>9.890000343322754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4763491724507283</v>
+        <v>0.3866176440360698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8101266026496887</v>
+        <v>0.7857142686843872</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7682775855064392</v>
+        <v>0.7799999713897705</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7580978870391846</v>
+        <v>0.7616475224494934</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7455955147743225</v>
+        <v>0.7582417726516724</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1618349105119705</v>
+        <v>0.1632511913776397</v>
       </c>
       <c r="K3" t="n">
-        <v>83.44208168983459</v>
+        <v>50.95697236061096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1411863183975219</v>
+        <v>0.1235049724578857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2530272912979125</v>
+        <v>0.2694076538085937</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2492813491821289</v>
+        <v>0.229848690032959</v>
       </c>
       <c r="O3" t="n">
-        <v>7.059315919876099</v>
+        <v>6.175248622894287</v>
       </c>
       <c r="P3" t="n">
-        <v>12.65136456489563</v>
+        <v>13.47038269042969</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.46406745910644</v>
+        <v>11.49243450164795</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-114457</t>
+          <t>20250727-001905</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>332.8731017112732</v>
+        <v>298.8714661598206</v>
       </c>
       <c r="D4" t="n">
-        <v>14.14000034332275</v>
+        <v>10.21000003814697</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4737830641916242</v>
+        <v>0.4192814019593325</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8441558480262756</v>
+        <v>0.8834356069564819</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8276729583740234</v>
+        <v>0.8330059051513672</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7554904818534851</v>
+        <v>0.8022598624229431</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.5628848075866699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1552743166685104</v>
+        <v>0.1721753478050232</v>
       </c>
       <c r="K4" t="n">
-        <v>81.54044270515442</v>
+        <v>121.491055727005</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1285418224334716</v>
+        <v>0.1236241483688354</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2423427534103393</v>
+        <v>0.268986210823059</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2322233247756958</v>
+        <v>0.2125107669830322</v>
       </c>
       <c r="O4" t="n">
-        <v>6.427091121673584</v>
+        <v>6.181207418441772</v>
       </c>
       <c r="P4" t="n">
-        <v>12.11713767051697</v>
+        <v>13.44931054115295</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.61116623878479</v>
+        <v>10.62553834915161</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-115317</t>
+          <t>20250727-002537</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>354.4334557056427</v>
+        <v>330.4653689861298</v>
       </c>
       <c r="D5" t="n">
-        <v>14.38000011444092</v>
+        <v>9.609999656677246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4844886740994832</v>
+        <v>0.3766988272468249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9135802388191224</v>
+        <v>0.8944099545478821</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8667512536048889</v>
+        <v>0.8598917722702026</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8293371200561523</v>
+        <v>0.8051391839981079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8271954655647278</v>
+        <v>0.8037116527557373</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1616420298814773</v>
+        <v>0.169652447104454</v>
       </c>
       <c r="K5" t="n">
-        <v>81.87707662582397</v>
+        <v>45.30689573287964</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1219769573211669</v>
+        <v>0.1278363323211669</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2485039758682251</v>
+        <v>0.2685544204711914</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2460435962677002</v>
+        <v>0.2183578443527221</v>
       </c>
       <c r="O5" t="n">
-        <v>6.09884786605835</v>
+        <v>6.39181661605835</v>
       </c>
       <c r="P5" t="n">
-        <v>12.42519879341126</v>
+        <v>13.42772102355957</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.30217981338501</v>
+        <v>10.91789221763611</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-120147</t>
+          <t>20250727-003411</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>338.5092058181763</v>
+        <v>367.793098449707</v>
       </c>
       <c r="D6" t="n">
-        <v>14.40999984741211</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4799970477819443</v>
+        <v>0.3977349203907781</v>
       </c>
       <c r="F6" t="n">
-        <v>0.761904776096344</v>
+        <v>0.8352941274642944</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6892733573913574</v>
+        <v>0.7735236883163452</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6949030756950378</v>
+        <v>0.7659574747085571</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7227241396903992</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1445047855377197</v>
+        <v>0.1685229688882827</v>
       </c>
       <c r="K6" t="n">
-        <v>75.34188175201416</v>
+        <v>74.37206101417542</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1173361301422119</v>
+        <v>0.1214347887039184</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2459795045852661</v>
+        <v>0.2717496633529663</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2363030862808227</v>
+        <v>0.2257570362091064</v>
       </c>
       <c r="O6" t="n">
-        <v>5.866806507110596</v>
+        <v>6.071739435195923</v>
       </c>
       <c r="P6" t="n">
-        <v>12.29897522926331</v>
+        <v>13.58748316764832</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.81515431404114</v>
+        <v>11.28785181045532</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-121040</t>
+          <t>20250727-004205</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>218.4417695999145</v>
+        <v>236.5885393619537</v>
       </c>
       <c r="D2" t="n">
-        <v>9.420000076293944</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3528880106155262</v>
+        <v>0.2260452752312024</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8074533939361572</v>
+        <v>0.8148148059844971</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7546468377113342</v>
+        <v>0.7316762208938599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7275320887565613</v>
+        <v>0.730053186416626</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4034416973590851</v>
+        <v>0.7063544988632202</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1657406836748123</v>
+        <v>0.1479138135910034</v>
       </c>
       <c r="K2" t="n">
-        <v>51.71897292137146</v>
+        <v>19.39977717399597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.132828140258789</v>
+        <v>0.0923221206665039</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2706057453155517</v>
+        <v>0.1298810482025146</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2194724607467651</v>
+        <v>0.1386210250854492</v>
       </c>
       <c r="O2" t="n">
-        <v>6.641407012939453</v>
+        <v>4.616106033325195</v>
       </c>
       <c r="P2" t="n">
-        <v>13.53028726577759</v>
+        <v>6.494052410125732</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.97362303733826</v>
+        <v>6.931051254272461</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-014047</t>
+          <t>20250728-042954</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>273.8070969581604</v>
+        <v>177.1631481647492</v>
       </c>
       <c r="D3" t="n">
-        <v>8.939999580383301</v>
+        <v>5.269999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3752178161774041</v>
+        <v>0.2400818698681318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8139534592628479</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7347715497016907</v>
+        <v>0.7677293419837952</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7390761375427246</v>
+        <v>0.7707006335258484</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.5753424763679504</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1541923135519027</v>
+        <v>0.1361701935529709</v>
       </c>
       <c r="K3" t="n">
-        <v>51.69777035713196</v>
+        <v>25.06409049034119</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1351667070388794</v>
+        <v>0.0932257270812988</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2735429954528808</v>
+        <v>0.1329637908935547</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2113992452621459</v>
+        <v>0.1401884603500366</v>
       </c>
       <c r="O3" t="n">
-        <v>6.75833535194397</v>
+        <v>4.661286354064941</v>
       </c>
       <c r="P3" t="n">
-        <v>13.67714977264404</v>
+        <v>6.648189544677734</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.5699622631073</v>
+        <v>7.009423017501831</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-014651</t>
+          <t>20250728-043518</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5467,53 +5467,53 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>233.1323249340057</v>
+        <v>123.2340452671051</v>
       </c>
       <c r="D4" t="n">
-        <v>9.199999809265137</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4373738394920216</v>
+        <v>0.3154574722744698</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6428571343421936</v>
+        <v>0.6391752362251282</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5815808773040771</v>
+        <v>0.5315694808959961</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5794392228126526</v>
+        <v>0.5449137687683105</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5602129101753235</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1631028056144714</v>
+        <v>0.1317401081323623</v>
       </c>
       <c r="K4" t="n">
-        <v>51.47537469863892</v>
+        <v>24.50191164016724</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1321434068679809</v>
+        <v>0.0875727796554565</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2667863321304321</v>
+        <v>0.1262876176834106</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2213334321975708</v>
+        <v>0.123685073852539</v>
       </c>
       <c r="O4" t="n">
-        <v>6.607170343399048</v>
+        <v>4.378638982772827</v>
       </c>
       <c r="P4" t="n">
-        <v>13.33931660652161</v>
+        <v>6.314380884170532</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.06667160987854</v>
+        <v>6.184253692626953</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-015349</t>
+          <t>20250728-043942</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>234.0298972129821</v>
+        <v>173.2273786067963</v>
       </c>
       <c r="D5" t="n">
-        <v>8.930000305175781</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3669088441272115</v>
+        <v>0.231732620871984</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8279569745063782</v>
+        <v>0.7455621361732483</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7833125591278076</v>
+        <v>0.6658146977424622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.793211817741394</v>
+        <v>0.6639838814735413</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6218130588531494</v>
+        <v>0.674854576587677</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1643192172050476</v>
+        <v>0.1339619308710098</v>
       </c>
       <c r="K5" t="n">
-        <v>52.17079114913941</v>
+        <v>18.70291233062744</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1287406969070434</v>
+        <v>0.1026614809036255</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2792008972167968</v>
+        <v>0.1404454517364502</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2167884111404419</v>
+        <v>0.1437458848953247</v>
       </c>
       <c r="O5" t="n">
-        <v>6.437034845352173</v>
+        <v>5.133074045181274</v>
       </c>
       <c r="P5" t="n">
-        <v>13.96004486083984</v>
+        <v>7.02227258682251</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.8394205570221</v>
+        <v>7.187294244766235</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-020007</t>
+          <t>20250728-044311</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C6" t="n">
-        <v>228.4284744262696</v>
+        <v>163.2248733043671</v>
       </c>
       <c r="D6" t="n">
-        <v>9.170000076293944</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4141235143639321</v>
+        <v>0.2503453310458891</v>
       </c>
       <c r="F6" t="n">
         <v>0.7284768223762512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6482958793640137</v>
+        <v>0.6382140517234802</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6269113421440125</v>
+        <v>0.6017699241638184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4279155135154724</v>
+        <v>0.2612244784832001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1626805514097213</v>
+        <v>0.1309667974710464</v>
       </c>
       <c r="K6" t="n">
-        <v>45.50455474853516</v>
+        <v>18.97529220581055</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1325853586196899</v>
+        <v>0.0992003631591796</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2662238216400146</v>
+        <v>0.1385098314285278</v>
       </c>
       <c r="N6" t="n">
-        <v>0.212495322227478</v>
+        <v>0.1402185726165771</v>
       </c>
       <c r="O6" t="n">
-        <v>6.629267930984497</v>
+        <v>4.960018157958984</v>
       </c>
       <c r="P6" t="n">
-        <v>13.31119108200073</v>
+        <v>6.925491571426392</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.6247661113739</v>
+        <v>7.010928630828857</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-020621</t>
+          <t>20250728-044726</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>126.2582674026489</v>
+        <v>220.7306456565857</v>
       </c>
       <c r="D2" t="n">
-        <v>3.240000009536743</v>
+        <v>8.069999694824219</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2460946340275847</v>
+        <v>0.324025828454454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.675000011920929</v>
+        <v>0.8427672982215881</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5876460671424866</v>
+        <v>0.7812080383300781</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5720309019088745</v>
+        <v>0.779046356678009</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2316684424877166</v>
+        <v>0.7487821578979492</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1577581465244293</v>
+        <v>0.1627688258886337</v>
       </c>
       <c r="K2" t="n">
-        <v>38.01990652084351</v>
+        <v>39.86488580703735</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1034246730804443</v>
+        <v>0.1136045217514038</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1298658847808838</v>
+        <v>0.192445387840271</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1313543510437011</v>
+        <v>0.1823938703536987</v>
       </c>
       <c r="O2" t="n">
-        <v>5.171233654022217</v>
+        <v>5.68022608757019</v>
       </c>
       <c r="P2" t="n">
-        <v>6.493294239044189</v>
+        <v>9.62226939201355</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.567717552185059</v>
+        <v>9.119693517684937</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-164615</t>
+          <t>20250729-075241</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>119.8326473236084</v>
+        <v>232.1477599143982</v>
       </c>
       <c r="D3" t="n">
-        <v>3.099999904632568</v>
+        <v>6.539999961853027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2660805586465569</v>
+        <v>0.3156614037660452</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6373626589775085</v>
+        <v>0.8780487775802612</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5213963985443115</v>
+        <v>0.8210923075675964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5236406326293945</v>
+        <v>0.8202880620956421</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.8092783689498901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1575406640768051</v>
+        <v>0.1638476252555847</v>
       </c>
       <c r="K3" t="n">
-        <v>35.11862897872925</v>
+        <v>40.15118408203125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09848477363586421</v>
+        <v>0.1030470895767212</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1342291116714477</v>
+        <v>0.1981553316116333</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1273343563079834</v>
+        <v>0.1963435411453247</v>
       </c>
       <c r="O3" t="n">
-        <v>4.924238681793213</v>
+        <v>5.15235447883606</v>
       </c>
       <c r="P3" t="n">
-        <v>6.711455583572388</v>
+        <v>9.907766580581663</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.36671781539917</v>
+        <v>9.817177057266235</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-165002</t>
+          <t>20250729-075818</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>124.6678538322449</v>
+        <v>211.2711756229401</v>
       </c>
       <c r="D4" t="n">
-        <v>3.240000009536743</v>
+        <v>7.739999771118164</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3207438640123189</v>
+        <v>0.3493564968046389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8488371968269348</v>
+        <v>0.6623376607894897</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7800982594490051</v>
+        <v>0.6030219793319702</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7796161770820618</v>
+        <v>0.6161948442459106</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2160427868366241</v>
+        <v>0.6130114197731018</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1367890834808349</v>
+        <v>0.1541443020105362</v>
       </c>
       <c r="K4" t="n">
-        <v>29.99912476539612</v>
+        <v>40.29788017272949</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0905116987228393</v>
+        <v>0.1027636098861694</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1339241743087768</v>
+        <v>0.1884178304672241</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1318654537200927</v>
+        <v>0.2048727130889892</v>
       </c>
       <c r="O4" t="n">
-        <v>4.525584936141968</v>
+        <v>5.138180494308472</v>
       </c>
       <c r="P4" t="n">
-        <v>6.696208715438843</v>
+        <v>9.420891523361206</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.593272686004639</v>
+        <v>10.24363565444946</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-165340</t>
+          <t>20250729-080408</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
-        <v>124.8262422084808</v>
+        <v>251.1461718082428</v>
       </c>
       <c r="D5" t="n">
-        <v>2.980000019073486</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2483856303824319</v>
+        <v>0.31097312271595</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6703910827636719</v>
+        <v>0.8888888955116272</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6042928099632263</v>
+        <v>0.8202984929084778</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5993568897247314</v>
+        <v>0.822600245475769</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.8038216829299927</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1414679139852523</v>
+        <v>0.1588008999824524</v>
       </c>
       <c r="K5" t="n">
-        <v>37.11915946006775</v>
+        <v>34.47662138938904</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0987282037734985</v>
+        <v>0.1027357006072998</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1348196840286254</v>
+        <v>0.1939204025268554</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1230877208709716</v>
+        <v>0.2144817876815795</v>
       </c>
       <c r="O5" t="n">
-        <v>4.936410188674927</v>
+        <v>5.13678503036499</v>
       </c>
       <c r="P5" t="n">
-        <v>6.740984201431274</v>
+        <v>9.696020126342772</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.154386043548584</v>
+        <v>10.72408938407898</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-165717</t>
+          <t>20250729-080937</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C6" t="n">
-        <v>123.113997220993</v>
+        <v>290.9975438117981</v>
       </c>
       <c r="D6" t="n">
-        <v>3.079999923706055</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3060154169797897</v>
+        <v>0.3238523334642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6883116960525513</v>
+        <v>0.8941176533699036</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5925925970077515</v>
+        <v>0.7818061709403992</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5872284173965454</v>
+        <v>0.787564754486084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0791618153452873</v>
+        <v>0.7763769030570984</v>
       </c>
       <c r="J6" t="n">
-        <v>0.141677126288414</v>
+        <v>0.1541349440813064</v>
       </c>
       <c r="K6" t="n">
-        <v>31.12704610824585</v>
+        <v>40.20166182518005</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1005789184570312</v>
+        <v>0.1064845752716064</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1307668924331665</v>
+        <v>0.1951909828186035</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1273000431060791</v>
+        <v>0.1905520296096801</v>
       </c>
       <c r="O6" t="n">
-        <v>5.028945922851562</v>
+        <v>5.324228763580322</v>
       </c>
       <c r="P6" t="n">
-        <v>6.538344621658325</v>
+        <v>9.759549140930176</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.365002155303955</v>
+        <v>9.527601480484009</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-170101</t>
+          <t>20250729-081536</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
-        <v>193.5874671936035</v>
+        <v>70.97072410583496</v>
       </c>
       <c r="D2" t="n">
-        <v>7.03000020980835</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3201803665380088</v>
+        <v>0.1373319969229076</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8407643437385559</v>
+        <v>0.8662420511245728</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7458100318908691</v>
+        <v>0.6977363228797913</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7394270300865173</v>
+        <v>0.680272102355957</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7339832782745361</v>
+        <v>0.6772968769073486</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1414996832609176</v>
+        <v>0.0989258661866188</v>
       </c>
       <c r="K2" t="n">
-        <v>33.40593242645264</v>
+        <v>8.517260313034058</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1089360475540161</v>
+        <v>0.07310235023498531</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1978141641616821</v>
+        <v>0.09952966690063469</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1962263965606689</v>
+        <v>0.1163409423828125</v>
       </c>
       <c r="O2" t="n">
-        <v>5.446802377700806</v>
+        <v>3.655117511749268</v>
       </c>
       <c r="P2" t="n">
-        <v>9.890708208084106</v>
+        <v>4.976483345031738</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.811319828033447</v>
+        <v>5.817047119140625</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-044446</t>
+          <t>20250730-083715</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>215.6463236808777</v>
+        <v>61.54387307167053</v>
       </c>
       <c r="D3" t="n">
-        <v>5.980000019073486</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3302978543858779</v>
+        <v>0.1380839378146801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8496732115745544</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7443105578422546</v>
+        <v>0.7447272539138794</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7225716114044189</v>
+        <v>0.7436456084251404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7162066698074341</v>
+        <v>0.7405247688293457</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1665559411048889</v>
+        <v>0.1113165467977523</v>
       </c>
       <c r="K3" t="n">
-        <v>40.04603862762451</v>
+        <v>13.90823268890381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1162909221649169</v>
+        <v>0.0782173919677734</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1979094457626342</v>
+        <v>0.1021198368072509</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1995221662521362</v>
+        <v>0.100840482711792</v>
       </c>
       <c r="O3" t="n">
-        <v>5.81454610824585</v>
+        <v>3.910869598388672</v>
       </c>
       <c r="P3" t="n">
-        <v>9.895472288131714</v>
+        <v>5.105991840362549</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.976108312606812</v>
+        <v>5.0420241355896</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-044952</t>
+          <t>20250730-083919</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>179.929550409317</v>
+        <v>81.89260482788086</v>
       </c>
       <c r="D4" t="n">
-        <v>6.610000133514404</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3888451231920973</v>
+        <v>0.1384350568810595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.8311688303947449</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7592955231666565</v>
+        <v>0.7029831409454346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7620286345481873</v>
+        <v>0.6758832335472107</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6460055112838745</v>
+        <v>0.669248640537262</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1317139565944671</v>
+        <v>0.117114633321762</v>
       </c>
       <c r="K4" t="n">
-        <v>40.84532189369202</v>
+        <v>13.67738747596741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1092383289337158</v>
+        <v>0.0666714763641357</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1837124252319336</v>
+        <v>0.09652966499328609</v>
       </c>
       <c r="N4" t="n">
-        <v>0.187297511100769</v>
+        <v>0.0954308462142944</v>
       </c>
       <c r="O4" t="n">
-        <v>5.461916446685791</v>
+        <v>3.333573818206787</v>
       </c>
       <c r="P4" t="n">
-        <v>9.18562126159668</v>
+        <v>4.826483249664307</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.364875555038452</v>
+        <v>4.771542310714722</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-045528</t>
+          <t>20250730-084122</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="C5" t="n">
-        <v>164.5837540626526</v>
+        <v>174.8908727169037</v>
       </c>
       <c r="D5" t="n">
-        <v>6.03000020980835</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3233266469577084</v>
+        <v>0.1382480656959601</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8481012582778931</v>
+        <v>0.8662420511245728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.800477921962738</v>
+        <v>0.7226427793502808</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7860560417175293</v>
+        <v>0.7114391326904297</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7692307829856873</v>
+        <v>0.7079645991325378</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1676580011844635</v>
+        <v>0.1131666675209999</v>
       </c>
       <c r="K5" t="n">
-        <v>39.43980717658997</v>
+        <v>14.1143856048584</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1237089776992797</v>
+        <v>0.0713082981109619</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1872012519836425</v>
+        <v>0.098280611038208</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1930879640579223</v>
+        <v>0.0975284004211425</v>
       </c>
       <c r="O5" t="n">
-        <v>6.185448884963989</v>
+        <v>3.565414905548096</v>
       </c>
       <c r="P5" t="n">
-        <v>9.360062599182127</v>
+        <v>4.9140305519104</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.654398202896118</v>
+        <v>4.876420021057129</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-050026</t>
+          <t>20250730-084345</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>184.4462296962738</v>
+        <v>121.9996652603149</v>
       </c>
       <c r="D6" t="n">
-        <v>6.420000076293945</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3418704614955551</v>
+        <v>0.1390636577075268</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7388535141944885</v>
+        <v>0.8589743375778198</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6872483491897583</v>
+        <v>0.7691237926483154</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6979310512542725</v>
+        <v>0.6590538620948792</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6354647278785706</v>
+        <v>0.6650446057319641</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1570842713117599</v>
+        <v>0.1003803238272667</v>
       </c>
       <c r="K6" t="n">
-        <v>33.91176271438599</v>
+        <v>13.59964609146118</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1119288492202758</v>
+        <v>0.0682198905944824</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1956580877304077</v>
+        <v>0.1054700565338134</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2011017370223999</v>
+        <v>0.09751205444335929</v>
       </c>
       <c r="O6" t="n">
-        <v>5.596442461013794</v>
+        <v>3.410994529724121</v>
       </c>
       <c r="P6" t="n">
-        <v>9.782904386520386</v>
+        <v>5.273502826690674</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.05508685112</v>
+        <v>4.875602722167969</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-050508</t>
+          <t>20250730-084742</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>46.30511403083801</v>
+        <v>94.51183247566225</v>
       </c>
       <c r="D2" t="n">
-        <v>1.710000038146973</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.138007569525923</v>
+        <v>0.2549477012173549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8354430198669434</v>
+        <v>0.9024389982223512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7391021251678467</v>
+        <v>0.8183606266975403</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7027427554130554</v>
+        <v>0.8112074732780457</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6909360885620117</v>
+        <v>0.8116710782051086</v>
       </c>
       <c r="J2" t="n">
-        <v>0.080309122800827</v>
+        <v>0.0901410654187202</v>
       </c>
       <c r="K2" t="n">
-        <v>10.06595468521118</v>
+        <v>30.16951012611389</v>
       </c>
       <c r="L2" t="n">
-        <v>0.086436219215393</v>
+        <v>0.0669495582580566</v>
       </c>
       <c r="M2" t="n">
-        <v>0.11449227809906</v>
+        <v>0.1719708633422851</v>
       </c>
       <c r="N2" t="n">
-        <v>0.113789792060852</v>
+        <v>0.1577975797653198</v>
       </c>
       <c r="O2" t="n">
-        <v>4.321810960769653</v>
+        <v>3.347477912902832</v>
       </c>
       <c r="P2" t="n">
-        <v>5.724613904953003</v>
+        <v>8.598543167114258</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.689489603042603</v>
+        <v>7.889878988265991</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-182454</t>
+          <t>20250731-012733</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8180582523346</v>
+        <v>78.91916489601135</v>
       </c>
       <c r="D3" t="n">
-        <v>1.710000038146973</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1382100090992693</v>
+        <v>0.2570579105522483</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8695651888847351</v>
+        <v>0.9202454090118408</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7472094297409058</v>
+        <v>0.8416169881820679</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7268722653388977</v>
+        <v>0.8473895788192749</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7302964329719543</v>
+        <v>0.8496291041374207</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0892038121819496</v>
+        <v>0.09693111479282369</v>
       </c>
       <c r="K3" t="n">
-        <v>15.30490565299988</v>
+        <v>30.15739393234253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0811192512512207</v>
+        <v>0.0734226322174072</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1063331842422485</v>
+        <v>0.1725898504257202</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1115720129013061</v>
+        <v>0.1490798568725586</v>
       </c>
       <c r="O3" t="n">
-        <v>4.055962562561035</v>
+        <v>3.671131610870361</v>
       </c>
       <c r="P3" t="n">
-        <v>5.316659212112427</v>
+        <v>8.629492521286011</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.578600645065308</v>
+        <v>7.45399284362793</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-182643</t>
+          <t>20250731-013031</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>86.20069885253906</v>
+        <v>74.31536078453064</v>
       </c>
       <c r="D4" t="n">
-        <v>1.690000057220459</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1343157105940453</v>
+        <v>0.2548681335934137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.887499988079071</v>
+        <v>0.8848484754562378</v>
       </c>
       <c r="G4" t="n">
-        <v>0.806810736656189</v>
+        <v>0.8325906991958618</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7793493866920471</v>
+        <v>0.8011323213577271</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6057529449462891</v>
+        <v>0.8123249411582947</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0904937237501144</v>
+        <v>0.0936743542551994</v>
       </c>
       <c r="K4" t="n">
-        <v>15.56106543540955</v>
+        <v>30.15403723716736</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0813312578201294</v>
+        <v>0.0697515773773193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1093748331069946</v>
+        <v>0.1703916406631469</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1105714559555053</v>
+        <v>0.1522418117523193</v>
       </c>
       <c r="O4" t="n">
-        <v>4.06656289100647</v>
+        <v>3.487578868865967</v>
       </c>
       <c r="P4" t="n">
-        <v>5.468741655349731</v>
+        <v>8.519582033157349</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.528572797775269</v>
+        <v>7.612090587615967</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-182835</t>
+          <t>20250731-013323</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>56.29761028289795</v>
+        <v>88.72926926612854</v>
       </c>
       <c r="D5" t="n">
-        <v>1.710000038146973</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1396192025582668</v>
+        <v>0.2558648687773857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8944099545478821</v>
+        <v>0.9113923907279968</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7945736646652222</v>
+        <v>0.8439086079597473</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7829131484031677</v>
+        <v>0.8222066164016724</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7533039450645447</v>
+        <v>0.821052610874176</v>
       </c>
       <c r="J5" t="n">
-        <v>0.095010869204998</v>
+        <v>0.0944592356681823</v>
       </c>
       <c r="K5" t="n">
-        <v>15.2733371257782</v>
+        <v>29.58695483207702</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08803205966949459</v>
+        <v>0.06925055027008049</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1073377609252929</v>
+        <v>0.1741947126388549</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1105300283432006</v>
+        <v>0.157323727607727</v>
       </c>
       <c r="O5" t="n">
-        <v>4.401602983474731</v>
+        <v>3.462527513504028</v>
       </c>
       <c r="P5" t="n">
-        <v>5.366888046264648</v>
+        <v>8.709735631942749</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.526501417160034</v>
+        <v>7.866186380386352</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-183108</t>
+          <t>20250731-013600</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C6" t="n">
-        <v>81.5609405040741</v>
+        <v>107.7620975971222</v>
       </c>
       <c r="D6" t="n">
-        <v>1.710000038146973</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.137663753263736</v>
+        <v>0.2580015501450924</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8774193525314331</v>
+        <v>0.9268292784690856</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8050000071525574</v>
+        <v>0.833224356174469</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8045363426208496</v>
+        <v>0.7886710166931152</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8018555045127869</v>
+        <v>0.7900874614715576</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0901643931865692</v>
+        <v>0.0939741432666778</v>
       </c>
       <c r="K6" t="n">
-        <v>15.15770220756531</v>
+        <v>29.78220844268799</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08046713352203359</v>
+        <v>0.06916874408721919</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1101455211639404</v>
+        <v>0.1706633234024047</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1199308490753173</v>
+        <v>0.1504096412658691</v>
       </c>
       <c r="O6" t="n">
-        <v>4.023356676101685</v>
+        <v>3.458437204360962</v>
       </c>
       <c r="P6" t="n">
-        <v>5.507276058197021</v>
+        <v>8.533166170120239</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.996542453765869</v>
+        <v>7.520482063293457</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-183311</t>
+          <t>20250731-013852</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>68.24783563613892</v>
+        <v>57.10480189323425</v>
       </c>
       <c r="D2" t="n">
-        <v>5.380000114440918</v>
+        <v>6.539999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1035724844837534</v>
+        <v>0.1470039426349103</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8765432238578796</v>
+        <v>0.8834356069564819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7148648500442505</v>
+        <v>0.7828418016433716</v>
       </c>
       <c r="H2" t="n">
-        <v>0.715423583984375</v>
+        <v>0.7766990065574646</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7108938694000244</v>
+        <v>0.7742837071418762</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0958844572305679</v>
+        <v>0.103766955435276</v>
       </c>
       <c r="K2" t="n">
-        <v>14.31846594810486</v>
+        <v>19.12963485717773</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0815378284454345</v>
+        <v>0.0708183097839355</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1028697204589843</v>
+        <v>0.1263781356811523</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1041262674331665</v>
+        <v>0.1303306436538696</v>
       </c>
       <c r="O2" t="n">
-        <v>4.076891422271729</v>
+        <v>3.540915489196777</v>
       </c>
       <c r="P2" t="n">
-        <v>5.143486022949219</v>
+        <v>6.318906784057617</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.206313371658325</v>
+        <v>6.516532182693481</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-080331</t>
+          <t>20250627-155136</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>55.53451538085938</v>
+        <v>63.41537308692932</v>
       </c>
       <c r="D3" t="n">
-        <v>5.360000133514404</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1058119500952737</v>
+        <v>0.1453375029000075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8129032254219055</v>
+        <v>0.8679245114326477</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6848602890968323</v>
+        <v>0.8134714961051941</v>
       </c>
       <c r="H3" t="n">
-        <v>0.680672287940979</v>
+        <v>0.8145266175270081</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6827537417411804</v>
+        <v>0.8190599083900452</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1727137416601181</v>
+        <v>0.0896379575133323</v>
       </c>
       <c r="K3" t="n">
-        <v>8.758638381958008</v>
+        <v>19.93363475799561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.089834303855896</v>
+        <v>0.06799694538116451</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1017633485794067</v>
+        <v>0.1236702489852905</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1082399177551269</v>
+        <v>0.1328284692764282</v>
       </c>
       <c r="O3" t="n">
-        <v>4.4917151927948</v>
+        <v>3.399847269058228</v>
       </c>
       <c r="P3" t="n">
-        <v>5.088167428970337</v>
+        <v>6.183512449264526</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.411995887756348</v>
+        <v>6.641423463821411</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-080543</t>
+          <t>20250627-155348</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>94.94044423103333</v>
+        <v>60.20433855056763</v>
       </c>
       <c r="D4" t="n">
-        <v>5.579999923706055</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1051536691474153</v>
+        <v>0.1436695421951404</v>
       </c>
       <c r="F4" t="n">
-        <v>0.875</v>
+        <v>0.8819875717163086</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7341606616973877</v>
+        <v>0.8049254417419434</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7369844317436218</v>
+        <v>0.8041504621505737</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7404426336288452</v>
+        <v>0.7950713634490967</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09321931749582291</v>
+        <v>0.1000428572297096</v>
       </c>
       <c r="K4" t="n">
-        <v>8.838185548782349</v>
+        <v>19.32123780250549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07370696067810049</v>
+        <v>0.0630412340164184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1015636873245239</v>
+        <v>0.1313858699798584</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1039049482345581</v>
+        <v>0.1303719043731689</v>
       </c>
       <c r="O4" t="n">
-        <v>3.685348033905029</v>
+        <v>3.152061700820923</v>
       </c>
       <c r="P4" t="n">
-        <v>5.078184366226196</v>
+        <v>6.56929349899292</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.195247411727905</v>
+        <v>6.518595218658447</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-080742</t>
+          <t>20250627-155607</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>85.51538062095642</v>
+        <v>47.30350089073181</v>
       </c>
       <c r="D5" t="n">
-        <v>5.360000133514404</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1039218828969058</v>
+        <v>0.1448302696700449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8205128312110901</v>
+        <v>0.8662420511245728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6452494859695435</v>
+        <v>0.803396463394165</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6309695839881897</v>
+        <v>0.8028720617294312</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6310469508171082</v>
+        <v>0.7982062697410583</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1301712244749069</v>
+        <v>0.1026168838143348</v>
       </c>
       <c r="K5" t="n">
-        <v>8.801992893218994</v>
+        <v>19.51875257492065</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0786416292190551</v>
+        <v>0.0730934810638427</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1095090723037719</v>
+        <v>0.1297949695587158</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1102014589309692</v>
+        <v>0.1316215562820434</v>
       </c>
       <c r="O5" t="n">
-        <v>3.932081460952759</v>
+        <v>3.654674053192138</v>
       </c>
       <c r="P5" t="n">
-        <v>5.475453615188599</v>
+        <v>6.489748477935791</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.510072946548462</v>
+        <v>6.581077814102173</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-081020</t>
+          <t>20250627-155822</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C6" t="n">
-        <v>94.64770317077635</v>
+        <v>48.10929942131042</v>
       </c>
       <c r="D6" t="n">
-        <v>5.360000133514404</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1038419009047619</v>
+        <v>0.1446521966545669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.818791925907135</v>
+        <v>0.8930817842483521</v>
       </c>
       <c r="G6" t="n">
-        <v>0.688524603843689</v>
+        <v>0.8039734959602356</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6614542603492737</v>
+        <v>0.7673048377037048</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6520376205444336</v>
+        <v>0.767870306968689</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1015561744570732</v>
+        <v>0.1155830696225166</v>
       </c>
       <c r="K6" t="n">
-        <v>8.666732788085938</v>
+        <v>19.33374428749084</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0732473373413085</v>
+        <v>0.06437265872955319</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1103557920455932</v>
+        <v>0.1251251649856567</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1087126874923706</v>
+        <v>0.130143027305603</v>
       </c>
       <c r="O6" t="n">
-        <v>3.66236686706543</v>
+        <v>3.218632936477661</v>
       </c>
       <c r="P6" t="n">
-        <v>5.517789602279663</v>
+        <v>6.256258249282837</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.43563437461853</v>
+        <v>6.507151365280151</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-081235</t>
+          <t>20250627-160025</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9080,53 +9080,53 @@
         <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>60.47449445724487</v>
+        <v>46.30511403083801</v>
       </c>
       <c r="D2" t="n">
-        <v>7.550000190734863</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1761781360421861</v>
+        <v>0.138007569525923</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9068322777748108</v>
+        <v>0.8354430198669434</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8106312155723572</v>
+        <v>0.7391021251678467</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8035591840744019</v>
+        <v>0.7027427554130554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.797520637512207</v>
+        <v>0.6909360885620117</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0856089815497398</v>
+        <v>0.080309122800827</v>
       </c>
       <c r="K2" t="n">
-        <v>29.87047076225281</v>
+        <v>10.06595468521118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08245561122894279</v>
+        <v>0.086436219215393</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1714078140258789</v>
+        <v>0.11449227809906</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1516344976425171</v>
+        <v>0.113789792060852</v>
       </c>
       <c r="O2" t="n">
-        <v>4.122780561447144</v>
+        <v>4.321810960769653</v>
       </c>
       <c r="P2" t="n">
-        <v>8.570390701293945</v>
+        <v>5.724613904953003</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.581724882125854</v>
+        <v>5.689489603042603</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-101002</t>
+          <t>20250701-182454</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>75.11859345436096</v>
+        <v>45.8180582523346</v>
       </c>
       <c r="D3" t="n">
-        <v>7.449999809265137</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1750735489185899</v>
+        <v>0.1382100090992693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9135802388191224</v>
+        <v>0.8695651888847351</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8483709096908569</v>
+        <v>0.7472094297409058</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8146027326583862</v>
+        <v>0.7268722653388977</v>
       </c>
       <c r="I3" t="n">
-        <v>0.80173659324646</v>
+        <v>0.7302964329719543</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0812578201293945</v>
+        <v>0.0892038121819496</v>
       </c>
       <c r="K3" t="n">
-        <v>30.1287567615509</v>
+        <v>15.30490565299988</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08586107730865471</v>
+        <v>0.0811192512512207</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1702829933166504</v>
+        <v>0.1063331842422485</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1495648193359375</v>
+        <v>0.1115720129013061</v>
       </c>
       <c r="O3" t="n">
-        <v>4.293053865432739</v>
+        <v>4.055962562561035</v>
       </c>
       <c r="P3" t="n">
-        <v>8.51414966583252</v>
+        <v>5.316659212112427</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.478240966796875</v>
+        <v>5.578600645065308</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-101227</t>
+          <t>20250701-182643</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C4" t="n">
-        <v>118.2024374008179</v>
+        <v>86.20069885253906</v>
       </c>
       <c r="D4" t="n">
-        <v>7.539999961853027</v>
+        <v>1.690000057220459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1762908609727254</v>
+        <v>0.1343157105940453</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9044585824012756</v>
+        <v>0.887499988079071</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8406169414520264</v>
+        <v>0.806810736656189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8045812249183655</v>
+        <v>0.7793493866920471</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8077198266983032</v>
+        <v>0.6057529449462891</v>
       </c>
       <c r="J4" t="n">
-        <v>0.088761493563652</v>
+        <v>0.0904937237501144</v>
       </c>
       <c r="K4" t="n">
-        <v>30.58147668838501</v>
+        <v>15.56106543540955</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0892734909057617</v>
+        <v>0.0813312578201294</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1738095378875732</v>
+        <v>0.1093748331069946</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1427067422866821</v>
+        <v>0.1105714559555053</v>
       </c>
       <c r="O4" t="n">
-        <v>4.463674545288086</v>
+        <v>4.06656289100647</v>
       </c>
       <c r="P4" t="n">
-        <v>8.690476894378662</v>
+        <v>5.468741655349731</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.135337114334106</v>
+        <v>5.528572797775269</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-101518</t>
+          <t>20250701-182835</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>86.92277717590332</v>
+        <v>56.29761028289795</v>
       </c>
       <c r="D5" t="n">
-        <v>7.46999979019165</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17719730130724</v>
+        <v>0.1396192025582668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.912500023841858</v>
+        <v>0.8944099545478821</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8005372881889343</v>
+        <v>0.7945736646652222</v>
       </c>
       <c r="H5" t="n">
-        <v>0.790035605430603</v>
+        <v>0.7829131484031677</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7866761088371277</v>
+        <v>0.7533039450645447</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1022596657276153</v>
+        <v>0.095010869204998</v>
       </c>
       <c r="K5" t="n">
-        <v>29.3261775970459</v>
+        <v>15.2733371257782</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0824314546585083</v>
+        <v>0.08803205966949459</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1731666040420532</v>
+        <v>0.1073377609252929</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1510451126098632</v>
+        <v>0.1105300283432006</v>
       </c>
       <c r="O5" t="n">
-        <v>4.121572732925415</v>
+        <v>4.401602983474731</v>
       </c>
       <c r="P5" t="n">
-        <v>8.658330202102661</v>
+        <v>5.366888046264648</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.552255630493164</v>
+        <v>5.526501417160034</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-101851</t>
+          <t>20250701-183108</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="C6" t="n">
-        <v>50.9212589263916</v>
+        <v>81.5609405040741</v>
       </c>
       <c r="D6" t="n">
-        <v>7.46999979019165</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1765729624491471</v>
+        <v>0.137663753263736</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8875739574432373</v>
+        <v>0.8774193525314331</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8244373202323914</v>
+        <v>0.8050000071525574</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8250652551651001</v>
+        <v>0.8045363426208496</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8238410353660583</v>
+        <v>0.8018555045127869</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0835130959749221</v>
+        <v>0.0901643931865692</v>
       </c>
       <c r="K6" t="n">
-        <v>29.93819713592529</v>
+        <v>15.15770220756531</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0843412780761718</v>
+        <v>0.08046713352203359</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1837518548965454</v>
+        <v>0.1101455211639404</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1601866102218627</v>
+        <v>0.1199308490753173</v>
       </c>
       <c r="O6" t="n">
-        <v>4.217063903808594</v>
+        <v>4.023356676101685</v>
       </c>
       <c r="P6" t="n">
-        <v>9.187592744827271</v>
+        <v>5.507276058197021</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.00933051109314</v>
+        <v>5.996542453765869</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-102153</t>
+          <t>20250701-183311</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
